--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260917.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260917.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.06%</t>
+          <t>10.05%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.40%</t>
+          <t>9.44%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.56%</t>
+          <t>6.49%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.71%</t>
+          <t>5.72%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.16%</t>
+          <t>4.30%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.13%</t>
+          <t>4.07%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.02%</t>
+          <t>4.05%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.54%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.29%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
@@ -902,46 +902,46 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>131,081,000</t>
+          <t>99,718,442</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>202610TX</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,767</t>
+          <t>26,729,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,39 +953,39 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>202610TX</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>233,108,056</t>
+          <t>1,767</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>26,729,000</t>
+          <t>131,081,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,22 +997,22 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>99,718,442</t>
+          <t>233,108,056</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
@@ -1078,51 +1078,51 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>29,496,000</t>
+          <t>99,033,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>99,033,000</t>
+          <t>29,496,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>10,154,933,766</t>
+          <t>10,132,136,383</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,348,589,829</t>
+          <t>6,489,596,429</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>-17,106,963</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
